--- a/outputs/evaluation/requirement/design/v1/CF_M01/second/CF_M01_req_eval.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M01/second/CF_M01_req_eval.xlsx
@@ -627,10 +627,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -763,6 +761,14 @@
           <t>The system shall allow authorized users to list the different playlogs in the system.</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Changed from User Story H4 to FR</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -776,6 +782,10 @@
           <t>Be able to list the different playlogs of the system</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,6 +816,14 @@
           <t>The system shall allow authorized users to list the different actions performed on platform entities.</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Changed from User Story H6 to FR</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -820,6 +838,10 @@
 platform entities</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -850,6 +872,14 @@
           <t>The system shall allow authorized users to list the different player connections in the system.</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Changed from User Story H5 to FR</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>FR</t>
@@ -863,6 +893,10 @@
           <t>Be able to list the different player connections in the system</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -898,6 +932,13 @@
           <t>C_03</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12f to QR</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -911,11 +952,14 @@
           <t>The platform scales dynamically with changes in connections simultaneous.</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>CF_M01_R22</t>
         </is>
       </c>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -951,6 +995,13 @@
           <t>C_05</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 15a to QR</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>QR</t>
@@ -969,11 +1020,9 @@
           <t>CF_M01_C05</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1009,6 +1058,13 @@
           <t>C_02</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12d to QR</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1027,11 +1083,9 @@
           <t>CF_M01_C02</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1067,6 +1121,13 @@
           <t>C_04</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12g to QR</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1080,11 +1141,14 @@
           <t>The system scales automatically as they go increasing the data.</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M01_R24</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1115,11 +1179,14 @@
           <t>Each action must have a date, client, user, and player assigned.</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1133,11 +1200,14 @@
           <t>Each action has an assigned date, client and player.</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M01_R06</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1168,11 +1238,14 @@
           <t>All actions must be performed on a platform entity.</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_06</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1186,11 +1259,14 @@
           <t>All actions must be related to an entity the platform.</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+          <t>CF_M01_R15</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1221,11 +1297,14 @@
           <t>The actions visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_13</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1239,11 +1318,14 @@
           <t>The actions that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CF_M01_R015</t>
-        </is>
-      </c>
+          <t>CF_M01_R15</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1274,6 +1356,14 @@
           <t>The system shall save the connections of the players.</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Changed from User Story H2 to FR</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1287,6 +1377,10 @@
           <t>System saves player connections</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1317,11 +1411,14 @@
           <t>The connections visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_11</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1335,11 +1432,14 @@
           <t>The connections that the user will be able to see will depend on the permissions it has.</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M01_R12</t>
         </is>
       </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1375,6 +1475,13 @@
           <t>C_01</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 12a to QR</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1388,11 +1495,14 @@
           <t>The system responds to any user action in less than 5 seconds.</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CF_M01_R018</t>
-        </is>
-      </c>
+          <t>CF_M01_R18</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1423,11 +1533,14 @@
           <t>The playlogs visible to the user shall depend on their assigned permissions.</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_09</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1441,11 +1554,14 @@
           <t>The playlogs that the user will be able to see will depend on the permissions it has</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M01_R09</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1476,11 +1592,14 @@
           <t>Each playlog must have a date, client, and player assigned.</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1494,11 +1613,14 @@
           <t>Each playlog has an assigned date, client, player.</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M01_R01</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1529,11 +1651,14 @@
           <t>Each connection must have a date, client, and player assigned.</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1547,11 +1672,14 @@
           <t>Each connection has an assigned date, client, player.</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1582,6 +1710,14 @@
           <t>The system shall save the playlogs of the players.</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Changed from User Story H1 to FR</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1595,6 +1731,10 @@
           <t>System saves the players' playlogs</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1630,6 +1770,13 @@
           <t>C_06</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Changed from Requisit 15c to QR</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1649,11 +1796,9 @@
           <t>CF_M01_C06</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Volere</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1684,6 +1829,14 @@
           <t>The system shall save the actions performed on the platform.</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Changed from User Story H3 to FR</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1697,6 +1850,10 @@
           <t>System saves the actions carried out on the platform</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1727,11 +1884,14 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>R_03</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>Criterion</t>
@@ -1745,11 +1905,14 @@
           <t>The connection status can only be connected or not connected.</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>CF_M01_R03</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
